--- a/artfynd/A 31803-2024 artfynd.xlsx
+++ b/artfynd/A 31803-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129960377</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129960269</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129960405</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129960341</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129960434</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31803-2024 artfynd.xlsx
+++ b/artfynd/A 31803-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129960377</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129960269</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129960405</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129960341</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129960434</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31803-2024 artfynd.xlsx
+++ b/artfynd/A 31803-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129960377</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129960269</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129960405</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129960341</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129960434</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31803-2024 artfynd.xlsx
+++ b/artfynd/A 31803-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129960377</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129960269</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129960405</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129960341</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129960434</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31803-2024 artfynd.xlsx
+++ b/artfynd/A 31803-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129960377</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129960269</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129960405</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129960341</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129960434</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31803-2024 artfynd.xlsx
+++ b/artfynd/A 31803-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129960377</v>
+        <v>129960269</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614008</v>
+        <v>614012</v>
       </c>
       <c r="R2" t="n">
-        <v>6806068</v>
+        <v>6806051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 70 plantor, 5 blomstänglar noterades</t>
+          <t>7 plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129960269</v>
+        <v>129960341</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614012</v>
+        <v>614025</v>
       </c>
       <c r="R3" t="n">
-        <v>6806051</v>
+        <v>6806062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>7 plantor</t>
+          <t>8 plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129960405</v>
+        <v>129960377</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613954</v>
+        <v>614008</v>
       </c>
       <c r="R4" t="n">
-        <v>6805987</v>
+        <v>6806068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>Minst 70 plantor, 5 blomstänglar noterades</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960341</v>
+        <v>129960405</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614025</v>
+        <v>613954</v>
       </c>
       <c r="R5" t="n">
-        <v>6806062</v>
+        <v>6805987</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>8 plantor</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
         <v>129960434</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31803-2024 artfynd.xlsx
+++ b/artfynd/A 31803-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960269</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960341</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960377</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,8 +1272,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960434</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>